--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487766_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487766_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2048</v>
+        <v>2.4612</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0864</v>
+        <v>2.4016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1183</v>
+        <v>0.0596</v>
       </c>
       <c r="G2" t="n">
         <v>0.5012</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2467</v>
+        <v>0.5032</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7112</v>
+        <v>1.0263</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4645</v>
+        <v>-0.5232</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4226</v>
+        <v>1.936</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5171</v>
+        <v>2.9547</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9054</v>
+        <v>-1.0188</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5007</v>
+        <v>0.79</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0533</v>
+        <v>1.9232</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4474</v>
+        <v>-1.1332</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2188</v>
+        <v>2.2477</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6612</v>
+        <v>2.8502</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5576</v>
+        <v>-0.6026</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2818</v>
+        <v>-1.4577</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3921</v>
+        <v>-0.927</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1102</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0812</v>
+        <v>0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2081</v>
+        <v>-2.7055</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>2.9137</v>
       </c>
       <c r="S3" t="n">
-        <v>2.072</v>
+        <v>-0.6896</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9441</v>
+        <v>0.0339</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1279</v>
+        <v>-0.7235</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.3787</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.633</v>
+        <v>1.7811</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1438</v>
+        <v>2.7029</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5107</v>
+        <v>-0.9218</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1369</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1456</v>
+        <v>1.2937</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2172</v>
+        <v>0.7763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9284</v>
+        <v>0.5174</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1309</v>
+        <v>1.1791</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0323</v>
+        <v>-0.6383</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9013</v>
+        <v>1.8173</v>
       </c>
       <c r="G5" t="n">
-        <v>0.79</v>
+        <v>-1.5007</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9232</v>
+        <v>-1.0533</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1332</v>
+        <v>-0.4474</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2477</v>
+        <v>-1.2188</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8502</v>
+        <v>-0.6612</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6026</v>
+        <v>-0.5576</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4577</v>
+        <v>-0.2818</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.927</v>
+        <v>-0.3921</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.1102</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>2.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7055</v>
+        <v>-0.2081</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9137</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4947</v>
+        <v>0.8285</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.7887</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.606</v>
+        <v>0.0398</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6275</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3787</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6717</v>
+        <v>0.8376</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0261</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6977</v>
+        <v>0.7565</v>
       </c>
       <c r="G6" t="n">
         <v>0.1331</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.169</v>
+        <v>-0.0031</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V6" t="n">
         <v>0.7076</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4035</v>
+        <v>-0.3779</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4832</v>
+        <v>-0.3108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3299</v>
@@ -1000,13 +1000,13 @@
         <v>2.0812</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0731</v>
+        <v>0.0987</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2701</v>
+        <v>0.4425</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.197</v>
+        <v>-0.3438</v>
       </c>
       <c r="V7" t="n">
         <v>0.4776</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.092</v>
+        <v>-0.6927</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1779</v>
+        <v>-0.7493</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0566</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7214</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3875</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2649</v>
+        <v>-0.2942</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1712</v>
+        <v>-0.703</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7627</v>
+        <v>-1.4412</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5914</v>
+        <v>0.7382</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2409</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7222</v>
+        <v>-0.254</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3308</v>
+        <v>-0.184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4967</v>
+        <v>-2.0116</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0205</v>
+        <v>-1.741</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4762</v>
+        <v>-0.2706</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0465</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0745</v>
+        <v>-0.5895</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1338</v>
+        <v>0.1458</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9407</v>
+        <v>-0.7352</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4384</v>
+        <v>-2.535</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9523</v>
+        <v>-2.137</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4861</v>
+        <v>-0.398</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8511</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6061</v>
+        <v>0.2973</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3791</v>
+        <v>0.4363</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.227</v>
+        <v>-0.139</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4966</v>
+        <v>-4.1187</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4695</v>
+        <v>-3.2971</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0271</v>
+        <v>-0.8216</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3852</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5683</v>
+        <v>-0.1904</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1338</v>
+        <v>0.0386</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4345</v>
+        <v>-0.229</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.021800000000001</v>
+        <v>-9.1609</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0476</v>
+        <v>-5.3335</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9742</v>
+        <v>-3.8274</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3363</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4581</v>
+        <v>0.319</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3603</v>
+        <v>1.0745</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9023</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9813</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.0572</v>
+        <v>-11.4048</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.1602</v>
+        <v>-7.507900000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-3.8971</v>
@@ -1546,13 +1546,13 @@
         <v>18.7307</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5738999999999997</v>
+        <v>1.2263</v>
       </c>
       <c r="T14" t="n">
-        <v>3.989000000000001</v>
+        <v>4.641500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.4151</v>
+        <v>-3.4152</v>
       </c>
       <c r="V14" t="n">
         <v>0.3714</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4458</v>
+        <v>7.599</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3287</v>
+        <v>4.2216</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1171</v>
+        <v>3.3774</v>
       </c>
       <c r="G15" t="n">
         <v>3.2766</v>
@@ -1624,13 +1624,13 @@
         <v>2.9137</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2088</v>
+        <v>0.3619</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6582</v>
+        <v>0.5511</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4494</v>
+        <v>-0.1891</v>
       </c>
       <c r="V15" t="n">
         <v>2.0874</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.7094</v>
+        <v>6.8332</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7251</v>
+        <v>3.6179</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9843</v>
+        <v>3.2153</v>
       </c>
       <c r="G16" t="n">
         <v>4.5111</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4906</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8539</v>
+        <v>0.7468</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3633</v>
+        <v>-0.1323</v>
       </c>
       <c r="V16" t="n">
         <v>1.2914</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7244</v>
+        <v>2.8672</v>
       </c>
       <c r="E17" t="n">
         <v>1.3834</v>
       </c>
       <c r="F17" t="n">
-        <v>1.341</v>
+        <v>1.4838</v>
       </c>
       <c r="G17" t="n">
         <v>3.665</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4005</v>
+        <v>-0.2577</v>
       </c>
       <c r="T17" t="n">
         <v>0.2048</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6054</v>
+        <v>-0.4625</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1238</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.935</v>
+        <v>1.7894</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5119</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4231</v>
+        <v>2.3514</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2474</v>
+        <v>1.587</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0236</v>
+        <v>-2.5759</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2238</v>
+        <v>4.1629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1863</v>
+        <v>0.8893</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3218</v>
+        <v>-1.9837</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1355</v>
+        <v>2.873</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0612</v>
+        <v>0.6977</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2982</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3594</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8333</v>
+        <v>0.3054</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0093</v>
+        <v>0.503</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1761</v>
+        <v>-0.1976</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9376</v>
+        <v>0.9376</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3351</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2218</v>
+        <v>0.723</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9906</v>
+        <v>0.3332</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2124</v>
+        <v>0.3898</v>
       </c>
       <c r="G19" t="n">
-        <v>1.587</v>
+        <v>1.2474</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5759</v>
+        <v>0.0236</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1629</v>
+        <v>1.2238</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8893</v>
+        <v>0.1863</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9837</v>
+        <v>0.3218</v>
       </c>
       <c r="L19" t="n">
-        <v>2.873</v>
+        <v>-0.1355</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6977</v>
+        <v>1.0612</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.2982</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3594</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2622</v>
+        <v>0.6213</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0743</v>
+        <v>0.8306</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3365</v>
+        <v>-0.2094</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9376</v>
+        <v>-0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1787</v>
+        <v>0.208</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1787</v>
+        <v>0.208</v>
       </c>
       <c r="G20" t="n">
         <v>-0.049</v>
@@ -2014,13 +2014,13 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3714</v>
+        <v>-0.2642</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="F21" t="n">
         <v>-0.1756</v>
@@ -2092,10 +2092,10 @@
         <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4815</v>
+        <v>-0.3743</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U21" t="n">
         <v>-0.2857</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.463</v>
+        <v>-1.5138</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.863</v>
+        <v>-2.4344</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3999</v>
+        <v>0.9206</v>
       </c>
       <c r="G23" t="n">
         <v>3.1417</v>
@@ -2248,13 +2248,13 @@
         <v>2.2893</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1698</v>
+        <v>-0.2205</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0743</v>
+        <v>0.503</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2441</v>
+        <v>-0.7235</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5213</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8744</v>
+        <v>-4.3068</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9376</v>
+        <v>-2.509</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9368</v>
+        <v>-1.7979</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7736</v>
@@ -2326,13 +2326,13 @@
         <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.747</v>
+        <v>-0.1794</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.199</v>
+        <v>0.2296</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.548</v>
+        <v>-0.409</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1051</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.0573</v>
+        <v>13.486</v>
       </c>
       <c r="E25" t="n">
-        <v>3.897000000000002</v>
+        <v>3.896899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>8.160300000000001</v>
+        <v>9.589</v>
       </c>
       <c r="G25" t="n">
         <v>16.1244</v>
       </c>
       <c r="H25" t="n">
-        <v>3.102499999999999</v>
+        <v>3.1025</v>
       </c>
       <c r="I25" t="n">
         <v>13.0219</v>
@@ -2404,22 +2404,22 @@
         <v>15.6089</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5738999999999997</v>
+        <v>0.8548</v>
       </c>
       <c r="T25" t="n">
-        <v>3.414900000000001</v>
+        <v>3.4151</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.9889</v>
+        <v>-2.5602</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3714000000000004</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7399</v>
+        <v>6.739900000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.1114</v>
+        <v>-7.111400000000001</v>
       </c>
     </row>
   </sheetData>
